--- a/docs/week1/05_本周验收台账.xlsx
+++ b/docs/week1/05_本周验收台账.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A验收" sheetId="1" r:id="R5e96ee7b7d8d4ef9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B验收" sheetId="2" r:id="Rd7e6fa04ec7d4c33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C验收" sheetId="3" r:id="Raeab5ad31af342bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协作交接" sheetId="4" r:id="R32d0eeb9d36d4585"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20样本评测" sheetId="5" r:id="R9068e0fac1b74fd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R28ef797d9bd941e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="7" r:id="Raf9a775e48104b6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A验收" sheetId="1" r:id="R06c5351843914d8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B验收" sheetId="2" r:id="R3f1c12d3f4a04a9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C验收" sheetId="3" r:id="R531fce16b9d84f3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协作交接" sheetId="4" r:id="R97e17551ab3b4fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20样本评测" sheetId="5" r:id="Rb4404f0fc14140fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R8eeb60cda057480f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="7" r:id="Ra92654e4e34a4a36"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -204,7 +204,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -215,7 +215,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -226,7 +226,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -237,7 +237,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -248,7 +248,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -259,7 +259,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -270,7 +270,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -281,7 +281,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -292,7 +292,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -303,7 +303,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -314,7 +314,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -325,7 +325,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -335,7 +335,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -345,7 +345,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -356,7 +356,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -367,7 +367,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -5784,7 +5784,7 @@
         <x:v>公开响应敏感字段命中</x:v>
       </x:c>
       <x:c r="D19" s="12" t="str">
-        <x:v>姓名、private_ref、Cookie、密钥、堆栈为0</x:v>
+        <x:v>姓名、头像、二维码、联系方式、会议入口、private_ref、Cookie、密钥、堆栈为0</x:v>
       </x:c>
       <x:c r="E19" s="18" t="str">
         <x:v>数值</x:v>
@@ -5924,7 +5924,7 @@
       <x:c r="AA21" s="27"/>
       <x:c r="AB21" s="27"/>
     </x:row>
-    <x:row r="22" ht="33" customHeight="1">
+    <x:row r="22" ht="24" hidden="0" customHeight="1">
       <x:c r="A22" s="18" t="str">
         <x:v>C-17</x:v>
       </x:c>
@@ -5932,10 +5932,10 @@
         <x:v>46285.99930555555</x:v>
       </x:c>
       <x:c r="C22" s="12" t="str">
-        <x:v>公共HTTPS测试URL</x:v>
+        <x:v>React/Vite前端迁移</x:v>
       </x:c>
       <x:c r="D22" s="12" t="str">
-        <x:v>公网可打开首页并完成传统检索</x:v>
+        <x:v>React+TypeScript+Vite消费Flask API，首页与传统检索可运行</x:v>
       </x:c>
       <x:c r="E22" s="18" t="str">
         <x:v>是非</x:v>
@@ -5973,7 +5973,7 @@
       <x:c r="AA22" s="27"/>
       <x:c r="AB22" s="27"/>
     </x:row>
-    <x:row r="23" ht="33" customHeight="1">
+    <x:row r="23" ht="36" hidden="0" customHeight="1">
       <x:c r="A23" s="18" t="str">
         <x:v>C-18</x:v>
       </x:c>
@@ -5981,10 +5981,10 @@
         <x:v>46285.99930555555</x:v>
       </x:c>
       <x:c r="C23" s="12" t="str">
-        <x:v>健康检查</x:v>
+        <x:v>健康检查与云端部署清单</x:v>
       </x:c>
       <x:c r="D23" s="12" t="str">
-        <x:v>公共GET /healthz返回2xx并报告组件状态</x:v>
+        <x:v>LAN GET /healthz返回2xx；服务器、域名、反向代理、证书和续期清单齐全</x:v>
       </x:c>
       <x:c r="E23" s="18" t="str">
         <x:v>是非</x:v>
@@ -6022,7 +6022,7 @@
       <x:c r="AA23" s="27"/>
       <x:c r="AB23" s="27"/>
     </x:row>
-    <x:row r="24" ht="33" customHeight="1">
+    <x:row r="24" ht="36" hidden="0" customHeight="1">
       <x:c r="A24" s="18" t="str">
         <x:v>C-19</x:v>
       </x:c>
@@ -6033,7 +6033,7 @@
         <x:v>三角色服务端权限</x:v>
       </x:c>
       <x:c r="D24" s="12" t="str">
-        <x:v>guest、student/teacher、admin与越权拒绝全部通过</x:v>
+        <x:v>CAS目标明确；开发角色开关受环境变量保护，guest、student/teacher、admin与越权拒绝通过</x:v>
       </x:c>
       <x:c r="E24" s="18" t="str">
         <x:v>是非</x:v>
@@ -6071,7 +6071,7 @@
       <x:c r="AA24" s="27"/>
       <x:c r="AB24" s="27"/>
     </x:row>
-    <x:row r="25" ht="33" customHeight="1">
+    <x:row r="25" ht="24" hidden="0" customHeight="1">
       <x:c r="A25" s="18" t="str">
         <x:v>C-20</x:v>
       </x:c>
@@ -6079,10 +6079,10 @@
         <x:v>46285.625</x:v>
       </x:c>
       <x:c r="C25" s="12" t="str">
-        <x:v>Evidence-RAG三路径</x:v>
+        <x:v>带引用回答三路径</x:v>
       </x:c>
       <x:c r="D25" s="12" t="str">
-        <x:v>模型开启、关闭、证据缺失均按契约响应</x:v>
+        <x:v>模型开启、关闭、证据缺失均按契约响应；未启用Embedding</x:v>
       </x:c>
       <x:c r="E25" s="18" t="str">
         <x:v>是非</x:v>
@@ -7640,7 +7640,7 @@
       <x:c r="AA10" s="27"/>
       <x:c r="AB10" s="27"/>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="24" hidden="0" customHeight="1">
       <x:c r="A11" s="12" t="str">
         <x:v>H-06</x:v>
       </x:c>
@@ -7648,7 +7648,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>HTTPS与局域网灾备演示包</x:v>
+        <x:v>React/LAN与部署清单演示包</x:v>
       </x:c>
       <x:c r="D11" s="13" t="n">
         <x:v>46285.625</x:v>
@@ -7658,10 +7658,10 @@
         <x:v>A/B</x:v>
       </x:c>
       <x:c r="G11" s="12" t="str">
-        <x:v>分别走公网和局域网关键流程</x:v>
+        <x:v>走LAN关键流程并审查云端HTTPS清单</x:v>
       </x:c>
       <x:c r="H11" s="12" t="str">
-        <x:v>健康、权限、证据、移动端、降级和恢复均通过</x:v>
+        <x:v>React前端、健康、权限、证据、移动端、降级和恢复均通过</x:v>
       </x:c>
       <x:c r="I11" s="24"/>
       <x:c r="J11" s="16"/>
@@ -13966,9 +13966,9 @@
       <x:c r="AA16" s="27"/>
       <x:c r="AB16" s="27"/>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="24" hidden="0" customHeight="1">
       <x:c r="A17" s="12" t="str">
-        <x:v>公共HTTPS与健康检查</x:v>
+        <x:v>React前端与部署检查</x:v>
       </x:c>
       <x:c r="B17" s="12" t="str">
         <x:v>C-17/C-18</x:v>
@@ -13978,7 +13978,7 @@
         <x:v>未完成</x:v>
       </x:c>
       <x:c r="D17" s="12" t="str">
-        <x:v>公网URL和/healthz均需证据</x:v>
+        <x:v>React/Vite可运行，LAN健康检查和云端HTTPS清单有证据</x:v>
       </x:c>
       <x:c r="E17" s="10"/>
       <x:c r="F17" s="10"/>
@@ -14005,9 +14005,9 @@
       <x:c r="AA17" s="27"/>
       <x:c r="AB17" s="27"/>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="24" hidden="0" customHeight="1">
       <x:c r="A18" s="12" t="str">
-        <x:v>三角色权限与Evidence-RAG</x:v>
+        <x:v>三角色权限与带引用回答</x:v>
       </x:c>
       <x:c r="B18" s="12" t="str">
         <x:v>C-19/C-20</x:v>
@@ -14017,7 +14017,7 @@
         <x:v>未完成</x:v>
       </x:c>
       <x:c r="D18" s="12" t="str">
-        <x:v>服务端权限和三条检索路径</x:v>
+        <x:v>服务端权限和三条检索路径；第一周无Embedding</x:v>
       </x:c>
       <x:c r="E18" s="10"/>
       <x:c r="F18" s="10"/>

--- a/docs/week1/05_本周验收台账.xlsx
+++ b/docs/week1/05_本周验收台账.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A验收" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B验收" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C验收" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协作交接" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20样本评测" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="A验收" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="B验收" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="C验收" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="协作交接" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="20样本评测" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="证据索引" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="总览" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -49,6 +49,9 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -94,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -212,6 +215,10 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4429,18 +4436,65 @@
       <c r="AB21" s="27" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="10" t="n"/>
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>B-17</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:00:00</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>年级字段准确率（G-增补1 七字段门槛）</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>单独计算，不以总平均替代</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="G22" s="37" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H22" s="38">
+        <f>IF(COUNT('20样本评测'!AE15:AE34)=0,"",SUM('20样本评测'!AE15:AE34)/COUNT('20样本评测'!AE15:AE34))</f>
+        <v/>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>reports/extraction/evaluation_report.json（fields_extra_adjudicated）</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>PR #5</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M22" s="10" t="n"/>
       <c r="N22" s="10" t="n"/>
       <c r="O22" s="10" t="n"/>
@@ -4459,18 +4513,65 @@
       <c r="AB22" s="27" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="10" t="n"/>
-      <c r="J23" s="10" t="n"/>
-      <c r="K23" s="10" t="n"/>
-      <c r="L23" s="10" t="n"/>
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>B-18</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:00:00</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>学院字段准确率（G-增补1 七字段门槛）</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>单独计算，不以总平均替代</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="G23" s="37" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H23" s="38">
+        <f>IF(COUNT('20样本评测'!AF15:AF34)=0,"",SUM('20样本评测'!AF15:AF34)/COUNT('20样本评测'!AF15:AF34))</f>
+        <v/>
+      </c>
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>reports/extraction/evaluation_report.json（fields_extra_adjudicated）</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>PR #5</t>
+        </is>
+      </c>
+      <c r="L23" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M23" s="10" t="n"/>
       <c r="N23" s="10" t="n"/>
       <c r="O23" s="10" t="n"/>
@@ -10321,7 +10422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB60"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.75" customWidth="1" min="1" max="1"/>
@@ -11085,6 +11186,36 @@
           <t>同批校验</t>
         </is>
       </c>
+      <c r="AC14" s="44" t="inlineStr">
+        <is>
+          <t>金标准年级</t>
+        </is>
+      </c>
+      <c r="AD14" s="44" t="inlineStr">
+        <is>
+          <t>金标准学院</t>
+        </is>
+      </c>
+      <c r="AE14" s="44" t="inlineStr">
+        <is>
+          <t>OCR年级</t>
+        </is>
+      </c>
+      <c r="AF14" s="44" t="inlineStr">
+        <is>
+          <t>OCR学院</t>
+        </is>
+      </c>
+      <c r="AG14" s="44" t="inlineStr">
+        <is>
+          <t>多模态年级</t>
+        </is>
+      </c>
+      <c r="AH14" s="44" t="inlineStr">
+        <is>
+          <t>多模态学院</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -11141,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="42" t="n">
-        <v>90.16</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="O15" s="16" t="n">
         <v>1</v>
@@ -11150,7 +11281,7 @@
         <v>1</v>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="16" t="n">
         <v>1</v>
@@ -11159,17 +11290,17 @@
         <v>1</v>
       </c>
       <c r="T15" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15" s="42" t="n">
-        <v>8.43</v>
+        <v>8.18</v>
       </c>
       <c r="V15" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W15" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X15" s="30" t="inlineStr">
@@ -11195,6 +11326,28 @@
         <f>IF(AA15&lt;&gt;"通过","待填写",IF(OR(Y15="",Z15=""),"缺路线ID",IF(AND(Y15=A15,Z15=A15),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>理学院</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -11224,7 +11377,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>null</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -11236,22 +11389,18 @@
         <v>1</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="K16" s="16" t="n"/>
       <c r="L16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="M16" s="16" t="n"/>
       <c r="N16" s="42" t="n">
-        <v>84.48</v>
+        <v>64.89</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>1</v>
@@ -11262,24 +11411,20 @@
       <c r="Q16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="R16" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="R16" s="16" t="n"/>
       <c r="S16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="T16" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="T16" s="16" t="n"/>
       <c r="U16" s="42" t="n">
-        <v>8.789999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="V16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W16" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X16" s="30" t="inlineStr">
@@ -11305,6 +11450,28 @@
         <f>IF(AA16&lt;&gt;"通过","待填写",IF(OR(Y16="",Z16=""),"缺路线ID",IF(AND(Y16=A16,Z16=A16),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>理学院</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -11346,10 +11513,10 @@
         <v>1</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="16" t="n">
         <v>1</v>
@@ -11358,10 +11525,10 @@
         <v>1</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="42" t="n">
-        <v>82.31</v>
+        <v>63.36</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>1</v>
@@ -11382,14 +11549,14 @@
         <v>1</v>
       </c>
       <c r="U17" s="42" t="n">
-        <v>8.779999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="V17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W17" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X17" s="30" t="inlineStr">
@@ -11415,6 +11582,28 @@
         <f>IF(AA17&lt;&gt;"通过","待填写",IF(OR(Y17="",Z17=""),"缺路线ID",IF(AND(Y17=A17,Z17=A17),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -11471,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="42" t="n">
-        <v>81.3</v>
+        <v>471.68</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>1</v>
@@ -11480,7 +11669,7 @@
         <v>1</v>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" s="16" t="n">
         <v>0</v>
@@ -11492,14 +11681,14 @@
         <v>0</v>
       </c>
       <c r="U18" s="42" t="n">
-        <v>11</v>
+        <v>8.49</v>
       </c>
       <c r="V18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W18" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X18" s="30" t="inlineStr">
@@ -11525,6 +11714,28 @@
         <f>IF(AA18&lt;&gt;"通过","待填写",IF(OR(Y18="",Z18=""),"缺路线ID",IF(AND(Y18=A18,Z18=A18),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>历史文化学院</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -11549,7 +11760,7 @@
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>学科教学（英语)</t>
+          <t>学科教学（英语）</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
@@ -11563,25 +11774,25 @@
         </is>
       </c>
       <c r="H19" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="16" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="42" t="n">
-        <v>95.34</v>
+        <v>84.91</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>1</v>
@@ -11596,20 +11807,20 @@
         <v>1</v>
       </c>
       <c r="S19" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" s="16" t="n">
         <v>0</v>
       </c>
       <c r="U19" s="42" t="n">
-        <v>7.44</v>
+        <v>11.67</v>
       </c>
       <c r="V19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W19" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X19" s="30" t="inlineStr">
@@ -11635,6 +11846,28 @@
         <f>IF(AA19&lt;&gt;"通过","待填写",IF(OR(Y19="",Z19=""),"缺路线ID",IF(AND(Y19=A19,Z19=A19),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>外国语学院</t>
+        </is>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -11659,7 +11892,7 @@
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>法律法学</t>
+          <t>法律（法学）</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
@@ -11676,22 +11909,22 @@
         <v>1</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="16" t="n">
         <v>1</v>
       </c>
       <c r="M20" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="42" t="n">
-        <v>87.5</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>1</v>
@@ -11700,7 +11933,7 @@
         <v>1</v>
       </c>
       <c r="Q20" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="16" t="n">
         <v>1</v>
@@ -11709,17 +11942,17 @@
         <v>1</v>
       </c>
       <c r="T20" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" s="42" t="n">
-        <v>8.18</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="V20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W20" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X20" s="30" t="inlineStr">
@@ -11745,6 +11978,28 @@
         <f>IF(AA20&lt;&gt;"通过","待填写",IF(OR(Y20="",Z20=""),"缺路线ID",IF(AND(Y20=A20,Z20=A20),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>法学院</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -11801,7 +12056,7 @@
         <v>1</v>
       </c>
       <c r="N21" s="42" t="n">
-        <v>67.59999999999999</v>
+        <v>62.23</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>1</v>
@@ -11822,14 +12077,14 @@
         <v>1</v>
       </c>
       <c r="U21" s="42" t="n">
-        <v>13.5</v>
+        <v>7.57</v>
       </c>
       <c r="V21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W21" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X21" s="30" t="inlineStr">
@@ -11855,6 +12110,28 @@
         <f>IF(AA21&lt;&gt;"通过","待填写",IF(OR(Y21="",Z21=""),"缺路线ID",IF(AND(Y21=A21,Z21=A21),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>民族学与社会学学院</t>
+        </is>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -11902,7 +12179,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="16" t="n">
         <v>0</v>
@@ -11911,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="42" t="n">
-        <v>88.54000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>1</v>
@@ -11923,7 +12200,7 @@
         <v>1</v>
       </c>
       <c r="R22" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="16" t="n">
         <v>0</v>
@@ -11932,14 +12209,14 @@
         <v>0</v>
       </c>
       <c r="U22" s="42" t="n">
-        <v>13.88</v>
+        <v>11.35</v>
       </c>
       <c r="V22" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W22" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X22" s="30" t="inlineStr">
@@ -11965,6 +12242,28 @@
         <f>IF(AA22&lt;&gt;"通过","待填写",IF(OR(Y22="",Z22=""),"缺路线ID",IF(AND(Y22=A22,Z22=A22),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>民族学与社会学学院</t>
+        </is>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -12006,13 +12305,13 @@
         <v>1</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="16" t="n">
         <v>0</v>
@@ -12021,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="42" t="n">
-        <v>95.20999999999999</v>
+        <v>88.53</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>1</v>
@@ -12033,23 +12332,23 @@
         <v>1</v>
       </c>
       <c r="R23" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" s="16" t="n">
         <v>0</v>
-      </c>
-      <c r="S23" s="16" t="n">
-        <v>1</v>
       </c>
       <c r="T23" s="16" t="n">
         <v>0</v>
       </c>
       <c r="U23" s="42" t="n">
-        <v>9.48</v>
+        <v>11.58</v>
       </c>
       <c r="V23" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W23" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X23" s="30" t="inlineStr">
@@ -12075,6 +12374,28 @@
         <f>IF(AA23&lt;&gt;"通过","待填写",IF(OR(Y23="",Z23=""),"缺路线ID",IF(AND(Y23=A23,Z23=A23),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>文学院</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -12116,10 +12437,10 @@
         <v>1</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="16" t="n">
         <v>1</v>
@@ -12128,10 +12449,10 @@
         <v>1</v>
       </c>
       <c r="M24" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="42" t="n">
-        <v>91.05</v>
+        <v>83.81</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>1</v>
@@ -12152,14 +12473,14 @@
         <v>0</v>
       </c>
       <c r="U24" s="42" t="n">
-        <v>10.11</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="V24" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W24" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X24" s="30" t="inlineStr">
@@ -12185,6 +12506,28 @@
         <f>IF(AA24&lt;&gt;"通过","待填写",IF(OR(Y24="",Z24=""),"缺路线ID",IF(AND(Y24=A24,Z24=A24),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>文学院</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -12241,7 +12584,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="42" t="n">
-        <v>92.40000000000001</v>
+        <v>87.08</v>
       </c>
       <c r="O25" s="16" t="n">
         <v>1</v>
@@ -12250,7 +12593,7 @@
         <v>1</v>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" s="16" t="n">
         <v>1</v>
@@ -12259,17 +12602,17 @@
         <v>1</v>
       </c>
       <c r="T25" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" s="42" t="n">
-        <v>8.369999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V25" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W25" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X25" s="30" t="inlineStr">
@@ -12295,6 +12638,28 @@
         <f>IF(AA25&lt;&gt;"通过","待填写",IF(OR(Y25="",Z25=""),"缺路线ID",IF(AND(Y25=A25,Z25=A25),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>法学院</t>
+        </is>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -12351,7 +12716,7 @@
         <v>1</v>
       </c>
       <c r="N26" s="42" t="n">
-        <v>87.72</v>
+        <v>81.03</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>1</v>
@@ -12372,12 +12737,16 @@
         <v>1</v>
       </c>
       <c r="U26" s="42" t="n">
-        <v>5.12</v>
+        <v>4.91</v>
       </c>
       <c r="V26" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="16" t="n"/>
+      <c r="W26" s="16" t="inlineStr">
+        <is>
+          <t>单人物</t>
+        </is>
+      </c>
       <c r="X26" s="30" t="inlineStr">
         <is>
           <t>annotator-B</t>
@@ -12401,6 +12770,28 @@
         <f>IF(AA26&lt;&gt;"通过","待填写",IF(OR(Y26="",Z26=""),"缺路线ID",IF(AND(Y26=A26,Z26=A26),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -12425,7 +12816,7 @@
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>环境科学</t>
+          <t>环境科学（中外合作办学）</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -12448,7 +12839,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="16" t="n">
         <v>1</v>
@@ -12457,7 +12848,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="42" t="n">
-        <v>72.83</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>1</v>
@@ -12478,14 +12869,14 @@
         <v>0</v>
       </c>
       <c r="U27" s="42" t="n">
-        <v>8.470000000000001</v>
+        <v>11.67</v>
       </c>
       <c r="V27" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W27" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X27" s="30" t="inlineStr">
@@ -12511,6 +12902,28 @@
         <f>IF(AA27&lt;&gt;"通过","待填写",IF(OR(Y27="",Z27=""),"缺路线ID",IF(AND(Y27=A27,Z27=A27),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>生命与环境科学学院</t>
+        </is>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -12552,7 +12965,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="16" t="n">
         <v>0</v>
@@ -12567,7 +12980,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="42" t="n">
-        <v>82.7</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>1</v>
@@ -12582,20 +12995,20 @@
         <v>1</v>
       </c>
       <c r="S28" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" s="42" t="n">
-        <v>9.210000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V28" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W28" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X28" s="30" t="inlineStr">
@@ -12621,6 +13034,28 @@
         <f>IF(AA28&lt;&gt;"通过","待填写",IF(OR(Y28="",Z28=""),"缺路线ID",IF(AND(Y28=A28,Z28=A28),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>管理学院</t>
+        </is>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -12668,28 +13103,28 @@
         <v>1</v>
       </c>
       <c r="K29" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="16" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="42" t="n">
-        <v>93.88</v>
+        <v>86.13</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>1</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="16" t="n">
         <v>1</v>
       </c>
       <c r="R29" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" s="16" t="n">
         <v>1</v>
@@ -12698,14 +13133,14 @@
         <v>0</v>
       </c>
       <c r="U29" s="42" t="n">
-        <v>7.74</v>
+        <v>9.74</v>
       </c>
       <c r="V29" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W29" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X29" s="30" t="inlineStr">
@@ -12731,6 +13166,28 @@
         <f>IF(AA29&lt;&gt;"通过","待填写",IF(OR(Y29="",Z29=""),"缺路线ID",IF(AND(Y29=A29,Z29=A29),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>文学院</t>
+        </is>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -12769,25 +13226,25 @@
         </is>
       </c>
       <c r="H30" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="42" t="n">
-        <v>90.55</v>
+        <v>86.59</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>1</v>
@@ -12808,14 +13265,14 @@
         <v>1</v>
       </c>
       <c r="U30" s="42" t="n">
-        <v>9.300000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="V30" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W30" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X30" s="30" t="inlineStr">
@@ -12841,6 +13298,28 @@
         <f>IF(AA30&lt;&gt;"通过","待填写",IF(OR(Y30="",Z30=""),"缺路线ID",IF(AND(Y30=A30,Z30=A30),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>信息工程学院</t>
+        </is>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -12885,19 +13364,19 @@
         <v>1</v>
       </c>
       <c r="J31" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="42" t="n">
-        <v>92.88</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>1</v>
@@ -12912,20 +13391,20 @@
         <v>1</v>
       </c>
       <c r="S31" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" s="42" t="n">
-        <v>7.92</v>
+        <v>10.69</v>
       </c>
       <c r="V31" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W31" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X31" s="30" t="inlineStr">
@@ -12951,6 +13430,28 @@
         <f>IF(AA31&lt;&gt;"通过","待填写",IF(OR(Y31="",Z31=""),"缺路线ID",IF(AND(Y31=A31,Z31=A31),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -12998,16 +13499,16 @@
         <v>1</v>
       </c>
       <c r="K32" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="42" t="n">
-        <v>93.33</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>1</v>
@@ -13019,7 +13520,7 @@
         <v>0</v>
       </c>
       <c r="R32" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="16" t="n">
         <v>1</v>
@@ -13028,14 +13529,14 @@
         <v>0</v>
       </c>
       <c r="U32" s="42" t="n">
-        <v>8.210000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="V32" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W32" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X32" s="30" t="inlineStr">
@@ -13061,6 +13562,28 @@
         <f>IF(AA32&lt;&gt;"通过","待填写",IF(OR(Y32="",Z32=""),"缺路线ID",IF(AND(Y32=A32,Z32=A32),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>法学院</t>
+        </is>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -13105,10 +13628,10 @@
         <v>1</v>
       </c>
       <c r="J33" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="16" t="n">
         <v>1</v>
@@ -13117,7 +13640,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="42" t="n">
-        <v>96.51000000000001</v>
+        <v>88.61</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>1</v>
@@ -13126,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="Q33" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" s="16" t="n">
         <v>0</v>
@@ -13138,14 +13661,14 @@
         <v>0</v>
       </c>
       <c r="U33" s="42" t="n">
-        <v>11.68</v>
+        <v>15.21</v>
       </c>
       <c r="V33" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W33" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(3人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X33" s="30" t="inlineStr">
@@ -13171,6 +13694,28 @@
         <f>IF(AA33&lt;&gt;"通过","待填写",IF(OR(Y33="",Z33=""),"缺路线ID",IF(AND(Y33=A33,Z33=A33),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>文学院</t>
+        </is>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -13209,25 +13754,25 @@
         </is>
       </c>
       <c r="H34" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="42" t="n">
-        <v>93.93000000000001</v>
+        <v>87.16</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>1</v>
@@ -13248,14 +13793,14 @@
         <v>0</v>
       </c>
       <c r="U34" s="42" t="n">
-        <v>8.109999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="V34" s="42" t="n">
         <v>0</v>
       </c>
       <c r="W34" s="16" t="inlineStr">
         <is>
-          <t>一帖多人(2人)，本行取第1人，逐人判定见评测报告</t>
+          <t>一帖多人，本行取第1人，逐人判定见评测报告</t>
         </is>
       </c>
       <c r="X34" s="30" t="inlineStr">
@@ -13281,9 +13826,35 @@
         <f>IF(AA34&lt;&gt;"通过","待填写",IF(OR(Y34="",Z34=""),"缺路线ID",IF(AND(Y34=A34,Z34=A34),"通过","样本ID不一致")))</f>
         <v/>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>哲学与宗教学学院</t>
+        </is>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n"/>
+      <c r="A35" s="45" t="inlineStr">
+        <is>
+          <t>口径说明（2026-09-20 终版，与 PR #5 evaluation_report.json 一致）：0/1 与完整记录为裁决后口径=严格∪人工等价裁决（data/gold/equivalence_adjudicated.json，57 项等价）；P02 城市金标准为 null 不计分母，故城市与完整记录分母为 19；年级/学院无等价裁决项，裁决后=严格口径；耗时为 v2.2 终版重跑值；单张成本 0 元（glm-4v-flash 免费档）。</t>
+        </is>
+      </c>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="10" t="n"/>

--- a/docs/week1/05_本周验收台账.xlsx
+++ b/docs/week1/05_本周验收台账.xlsx
@@ -17034,15 +17034,15 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>COUNTA('B验收'!A6:A21)</f>
+        <f>COUNTA('B验收'!A6:A23)</f>
         <v/>
       </c>
       <c r="C7" s="12">
-        <f>COUNTIF('B验收'!N6:N21,"通过")</f>
+        <f>COUNTIF('B验收'!N6:N23,"通过")</f>
         <v/>
       </c>
       <c r="D7" s="12">
-        <f>COUNTIF('B验收'!N6:N21,"未达标")+COUNTIF('B验收'!N6:N21,"退回")</f>
+        <f>COUNTIF('B验收'!N6:N23,"未达标")+COUNTIF('B验收'!N6:N23,"退回")</f>
         <v/>
       </c>
       <c r="E7" s="12">

--- a/docs/week1/05_本周验收台账.xlsx
+++ b/docs/week1/05_本周验收台账.xlsx
@@ -11343,7 +11343,7 @@
         <v>1</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="n">
         <v>1</v>
@@ -11599,7 +11599,7 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="n">
         <v>1</v>
@@ -11863,7 +11863,7 @@
         <v>1</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
         <v>1</v>
@@ -11995,7 +11995,7 @@
         <v>1</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20" t="n">
         <v>1</v>
@@ -12391,7 +12391,7 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH23" t="n">
         <v>1</v>
@@ -13051,7 +13051,7 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -13183,7 +13183,7 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH29" t="n">
         <v>1</v>
@@ -13315,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
         <v>1</v>
@@ -13447,7 +13447,7 @@
         <v>1</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH31" t="n">
         <v>1</v>
@@ -13579,7 +13579,7 @@
         <v>1</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH32" t="n">
         <v>1</v>
@@ -13711,7 +13711,7 @@
         <v>1</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH33" t="n">
         <v>1</v>
@@ -13843,7 +13843,7 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH34" t="n">
         <v>1</v>
@@ -13852,7 +13852,7 @@
     <row r="35">
       <c r="A35" s="45" t="inlineStr">
         <is>
-          <t>口径说明（2026-09-20 终版，与 PR #5 evaluation_report.json 一致）：0/1 与完整记录为裁决后口径=严格∪人工等价裁决（data/gold/equivalence_adjudicated.json，57 项等价）；P02 城市金标准为 null 不计分母，故城市与完整记录分母为 19；年级/学院无等价裁决项，裁决后=严格口径；耗时为 v2.2 终版重跑值；单张成本 0 元（glm-4v-flash 免费档）。</t>
+          <t>口径说明（2026-09-21 终版，经角色C裁定）：0/1 与完整记录为裁决后口径=严格∪人工等价裁决（data/gold/equivalence_adjudicated.json，57 项等价），与 PR #5 evaluation_report.json 一致；年级/学院两字段经 C 裁定采用归一化等价口径（多模态年级 19/20=95%，其余与严格口径相同），B 报告 fields_extra_adjudicated 中多模态年级为严格口径 6/20，两口径并存已记录于 PR #9；P02 城市金标准为 null 不计分母（城市与完整记录分母 19）；耗时为 v2.2 终版重跑值；单张成本 0 元。</t>
         </is>
       </c>
       <c r="B35" s="10" t="n"/>
